--- a/navigation_log.xlsx
+++ b/navigation_log.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="6" showHorizontalScroll="1" showVerticalScroll="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="7" showHorizontalScroll="1" showVerticalScroll="1"/>
   </bookViews>
   <sheets>
     <sheet name="Weather &amp; Flight Plan" sheetId="1" state="visible" r:id="rId2"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="400">
   <si>
     <t xml:space="preserve">Weather Log</t>
   </si>
@@ -1081,7 +1081,7 @@
     <t xml:space="preserve">FLIGHT HISTORY  (rows added by LogFlight macro)</t>
   </si>
   <si>
-    <t xml:space="preserve">LOGFLIGHT MACRO  —  OnlyOffice: View &gt; Macros &gt; New Macro &gt; paste code &gt; Run</t>
+    <t xml:space="preserve">LOGFLIGHT MACRO  —  OnlyOffice: View &gt; Macros &gt; New Macro &gt; paste code &gt; Run or Assign to Button/Graphic</t>
   </si>
   <si>
     <r>
@@ -2166,6 +2166,66 @@
   </si>
   <si>
     <t>})();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOGFLIGHT MACRO  —  Excel: You will need a premium version of excel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub LogFlight()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dim ws As Worksheet: Set ws = Sheets("Pilot Log")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Dim nextRow As Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    nextRow = ws.Cells(ws.Rows.Count, "A").End(xlUp).Row + 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ' Copy row 4 (Staging) to the next empty row in history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ws.Range("A4:U4").Copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ws.Cells(nextRow, 1).PasteSpecial Paste:=xlPasteValues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Application.CutCopyMode = False</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    MsgBox "Flight Logged Successfully!"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End Sub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOGFLIGHT MACRO  —  Google Sheets: Extensions &gt; Apps Script &gt; paste code &gt; Run or Assign to Button/Graphic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">function logFlight() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var ss = SpreadsheetApp.getActiveSpreadsheet();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var sheet = ss.getSheetByName("Pilot Log");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var data = sheet.getRange("A4:U4").getValues();</t>
+  </si>
+  <si>
+    <t>sheet.appendRow(data[0]);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpreadsheetApp.getUi().alert("Flight Logged Successfully!");</t>
+  </si>
+  <si>
+    <t>}</t>
   </si>
 </sst>
 </file>
@@ -2188,7 +2248,7 @@
     <numFmt numFmtId="176" formatCode="0&quot; KIAS&quot;"/>
     <numFmt numFmtId="177" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="41">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -2365,8 +2425,48 @@
       <color indexed="17"/>
       <name val="Courier New"/>
     </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="17"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="18"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color indexed="17"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color indexed="18"/>
+      <name val="Consolas"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2431,6 +2531,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -2718,7 +2824,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="153">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3075,11 +3181,14 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="26" fillId="12" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="27" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="28" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3093,6 +3202,36 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="32" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="26" fillId="13" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="33" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="34" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="35" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="36" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="37" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="38" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="39" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="40" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -8897,7 +9036,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{001800D9-000D-46C9-8E41-00FA0041000D}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{000A005C-00A4-48D7-875B-005B00B10072}">
             <xm:f>"NO-GO"</xm:f>
             <x14:dxf>
               <fill>
@@ -8911,7 +9050,7 @@
           <xm:sqref>C36:D36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{00860047-0038-4F75-9E4A-007E00A10022}">
+          <x14:cfRule type="cellIs" priority="3" operator="equal" id="{002D0045-0013-439E-9A65-00BD002700EE}">
             <xm:f>"GO"</xm:f>
             <x14:dxf>
               <fill>
@@ -8925,7 +9064,7 @@
           <xm:sqref>C36:D36</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="greaterThan" id="{009C0032-0035-4933-8DBD-007F00BE0039}">
+          <x14:cfRule type="cellIs" priority="1" operator="greaterThan" id="{008400AD-00EF-459D-B7EA-007300580072}">
             <xm:f>0</xm:f>
             <x14:dxf>
               <fill>
@@ -9161,253 +9300,949 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="110"/>
+    <col customWidth="1" min="1" max="11" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="135" t="s">
         <v>349</v>
       </c>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="136" t="s">
         <v>350</v>
       </c>
+      <c r="B2" s="137"/>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="136" t="s">
         <v>351</v>
       </c>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="137"/>
+      <c r="I3" s="137"/>
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="137" t="s">
+      <c r="A4" s="138" t="s">
         <v>352</v>
       </c>
+      <c r="B4" s="137"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="138" t="s">
         <v>353</v>
       </c>
+      <c r="B5" s="137"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="137"/>
+      <c r="K5" s="137"/>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="138" t="s">
         <v>354</v>
       </c>
+      <c r="B6" s="137"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="137"/>
+      <c r="F6" s="137"/>
+      <c r="G6" s="137"/>
+      <c r="H6" s="137"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="137"/>
+      <c r="K6" s="137"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="138" t="s">
         <v>355</v>
       </c>
+      <c r="B7" s="137"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="137"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="137"/>
+      <c r="G7" s="137"/>
+      <c r="H7" s="137"/>
+      <c r="I7" s="137"/>
+      <c r="J7" s="137"/>
+      <c r="K7" s="137"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="138"/>
+      <c r="A8" s="139"/>
+      <c r="B8" s="137"/>
+      <c r="C8" s="137"/>
+      <c r="D8" s="137"/>
+      <c r="E8" s="137"/>
+      <c r="F8" s="137"/>
+      <c r="G8" s="137"/>
+      <c r="H8" s="137"/>
+      <c r="I8" s="137"/>
+      <c r="J8" s="137"/>
+      <c r="K8" s="137"/>
     </row>
     <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="139" t="s">
+      <c r="A9" s="140" t="s">
         <v>356</v>
       </c>
+      <c r="B9" s="137"/>
+      <c r="C9" s="137"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="137"/>
+      <c r="H9" s="137"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="137"/>
+      <c r="K9" s="137"/>
     </row>
     <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="139" t="s">
+      <c r="A10" s="140" t="s">
         <v>357</v>
       </c>
+      <c r="B10" s="137"/>
+      <c r="C10" s="137"/>
+      <c r="D10" s="137"/>
+      <c r="E10" s="137"/>
+      <c r="F10" s="137"/>
+      <c r="G10" s="137"/>
+      <c r="H10" s="137"/>
+      <c r="I10" s="137"/>
+      <c r="J10" s="137"/>
+      <c r="K10" s="137"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="136" t="s">
         <v>358</v>
       </c>
+      <c r="B11" s="137"/>
+      <c r="C11" s="137"/>
+      <c r="D11" s="137"/>
+      <c r="E11" s="137"/>
+      <c r="F11" s="137"/>
+      <c r="G11" s="137"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="137"/>
+      <c r="J11" s="137"/>
+      <c r="K11" s="137"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="136" t="s">
         <v>359</v>
       </c>
+      <c r="B12" s="137"/>
+      <c r="C12" s="137"/>
+      <c r="D12" s="137"/>
+      <c r="E12" s="137"/>
+      <c r="F12" s="137"/>
+      <c r="G12" s="137"/>
+      <c r="H12" s="137"/>
+      <c r="I12" s="137"/>
+      <c r="J12" s="137"/>
+      <c r="K12" s="137"/>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="137" t="s">
+      <c r="A13" s="138" t="s">
         <v>360</v>
       </c>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="137"/>
+      <c r="F13" s="137"/>
+      <c r="G13" s="137"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="137"/>
+      <c r="J13" s="137"/>
+      <c r="K13" s="137"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="136" t="s">
         <v>361</v>
       </c>
+      <c r="B14" s="137"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="137"/>
+      <c r="E14" s="137"/>
+      <c r="F14" s="137"/>
+      <c r="G14" s="137"/>
+      <c r="H14" s="137"/>
+      <c r="I14" s="137"/>
+      <c r="J14" s="137"/>
+      <c r="K14" s="137"/>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="140"/>
+      <c r="A15" s="141"/>
+      <c r="B15" s="137"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="137"/>
+      <c r="G15" s="137"/>
+      <c r="H15" s="137"/>
+      <c r="I15" s="137"/>
+      <c r="J15" s="137"/>
+      <c r="K15" s="137"/>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="139" t="s">
+      <c r="A16" s="140" t="s">
         <v>362</v>
       </c>
+      <c r="B16" s="137"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="137"/>
+      <c r="H16" s="137"/>
+      <c r="I16" s="137"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="137"/>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="139" t="s">
+      <c r="A17" s="140" t="s">
         <v>363</v>
       </c>
+      <c r="B17" s="137"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
+      <c r="H17" s="137"/>
+      <c r="I17" s="137"/>
+      <c r="J17" s="137"/>
+      <c r="K17" s="137"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="136" t="s">
         <v>364</v>
       </c>
+      <c r="B18" s="137"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="137"/>
+      <c r="H18" s="137"/>
+      <c r="I18" s="137"/>
+      <c r="J18" s="137"/>
+      <c r="K18" s="137"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="137" t="s">
+      <c r="A19" s="138" t="s">
         <v>365</v>
       </c>
+      <c r="B19" s="137"/>
+      <c r="C19" s="137"/>
+      <c r="D19" s="137"/>
+      <c r="E19" s="137"/>
+      <c r="F19" s="137"/>
+      <c r="G19" s="137"/>
+      <c r="H19" s="137"/>
+      <c r="I19" s="137"/>
+      <c r="J19" s="137"/>
+      <c r="K19" s="137"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="139" t="s">
+      <c r="A20" s="140" t="s">
         <v>366</v>
       </c>
+      <c r="B20" s="137"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
+      <c r="H20" s="137"/>
+      <c r="I20" s="137"/>
+      <c r="J20" s="137"/>
+      <c r="K20" s="137"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="136" t="s">
         <v>367</v>
       </c>
+      <c r="B21" s="137"/>
+      <c r="C21" s="137"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="137"/>
+      <c r="I21" s="137"/>
+      <c r="J21" s="137"/>
+      <c r="K21" s="137"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="139" t="s">
+      <c r="A22" s="140" t="s">
         <v>368</v>
       </c>
+      <c r="B22" s="137"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="137"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="137"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="138"/>
+      <c r="A23" s="139"/>
+      <c r="B23" s="137"/>
+      <c r="C23" s="137"/>
+      <c r="D23" s="137"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="137"/>
+      <c r="G23" s="137"/>
+      <c r="H23" s="137"/>
+      <c r="I23" s="137"/>
+      <c r="J23" s="137"/>
+      <c r="K23" s="137"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="136" t="s">
         <v>369</v>
       </c>
+      <c r="B24" s="137"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="137"/>
+      <c r="H24" s="137"/>
+      <c r="I24" s="137"/>
+      <c r="J24" s="137"/>
+      <c r="K24" s="137"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="138"/>
+      <c r="A25" s="139"/>
+      <c r="B25" s="137"/>
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
+      <c r="H25" s="137"/>
+      <c r="I25" s="137"/>
+      <c r="J25" s="137"/>
+      <c r="K25" s="137"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="136" t="s">
         <v>370</v>
       </c>
+      <c r="B26" s="137"/>
+      <c r="C26" s="137"/>
+      <c r="D26" s="137"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="137"/>
+      <c r="G26" s="137"/>
+      <c r="H26" s="137"/>
+      <c r="I26" s="137"/>
+      <c r="J26" s="137"/>
+      <c r="K26" s="137"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="136" t="s">
         <v>371</v>
       </c>
+      <c r="B27" s="137"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="137"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="137"/>
+      <c r="I27" s="137"/>
+      <c r="J27" s="137"/>
+      <c r="K27" s="137"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="137" t="s">
+      <c r="A28" s="138" t="s">
         <v>372</v>
       </c>
+      <c r="B28" s="137"/>
+      <c r="C28" s="137"/>
+      <c r="D28" s="137"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="137"/>
+      <c r="G28" s="137"/>
+      <c r="H28" s="137"/>
+      <c r="I28" s="137"/>
+      <c r="J28" s="137"/>
+      <c r="K28" s="137"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="136" t="s">
         <v>373</v>
       </c>
+      <c r="B29" s="137"/>
+      <c r="C29" s="137"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="137"/>
+      <c r="G29" s="137"/>
+      <c r="H29" s="137"/>
+      <c r="I29" s="137"/>
+      <c r="J29" s="137"/>
+      <c r="K29" s="137"/>
     </row>
     <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="139" t="s">
+      <c r="A30" s="140" t="s">
         <v>374</v>
       </c>
+      <c r="B30" s="137"/>
+      <c r="C30" s="137"/>
+      <c r="D30" s="137"/>
+      <c r="E30" s="137"/>
+      <c r="F30" s="137"/>
+      <c r="G30" s="137"/>
+      <c r="H30" s="137"/>
+      <c r="I30" s="137"/>
+      <c r="J30" s="137"/>
+      <c r="K30" s="137"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="139" t="s">
+      <c r="A31" s="140" t="s">
         <v>375</v>
       </c>
+      <c r="B31" s="137"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="137"/>
+      <c r="F31" s="137"/>
+      <c r="G31" s="137"/>
+      <c r="H31" s="137"/>
+      <c r="I31" s="137"/>
+      <c r="J31" s="137"/>
+      <c r="K31" s="137"/>
     </row>
     <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="139" t="s">
+      <c r="A32" s="140" t="s">
         <v>372</v>
       </c>
+      <c r="B32" s="137"/>
+      <c r="C32" s="137"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="137"/>
+      <c r="H32" s="137"/>
+      <c r="I32" s="137"/>
+      <c r="J32" s="137"/>
+      <c r="K32" s="137"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="136" t="s">
         <v>376</v>
       </c>
+      <c r="B33" s="137"/>
+      <c r="C33" s="137"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="137"/>
+      <c r="F33" s="137"/>
+      <c r="G33" s="137"/>
+      <c r="H33" s="137"/>
+      <c r="I33" s="137"/>
+      <c r="J33" s="137"/>
+      <c r="K33" s="137"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="136" t="s">
         <v>377</v>
       </c>
+      <c r="B34" s="137"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="137"/>
+      <c r="F34" s="137"/>
+      <c r="G34" s="137"/>
+      <c r="H34" s="137"/>
+      <c r="I34" s="137"/>
+      <c r="J34" s="137"/>
+      <c r="K34" s="137"/>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="138"/>
+      <c r="A35" s="139"/>
+      <c r="B35" s="137"/>
+      <c r="C35" s="137"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="137"/>
+      <c r="G35" s="137"/>
+      <c r="H35" s="137"/>
+      <c r="I35" s="137"/>
+      <c r="J35" s="137"/>
+      <c r="K35" s="137"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="136" t="s">
         <v>378</v>
       </c>
+      <c r="B36" s="137"/>
+      <c r="C36" s="137"/>
+      <c r="D36" s="137"/>
+      <c r="E36" s="137"/>
+      <c r="F36" s="137"/>
+      <c r="G36" s="137"/>
+      <c r="H36" s="137"/>
+      <c r="I36" s="137"/>
+      <c r="J36" s="137"/>
+      <c r="K36" s="137"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="141"/>
+      <c r="A37" s="142"/>
+      <c r="B37" s="137"/>
+      <c r="C37" s="137"/>
+      <c r="D37" s="137"/>
+      <c r="E37" s="137"/>
+      <c r="F37" s="137"/>
+      <c r="G37" s="137"/>
+      <c r="H37" s="137"/>
+      <c r="I37" s="137"/>
+      <c r="J37" s="137"/>
+      <c r="K37" s="137"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="136" t="s">
         <v>379</v>
       </c>
+      <c r="B38" s="137"/>
+      <c r="C38" s="137"/>
+      <c r="D38" s="137"/>
+      <c r="E38" s="137"/>
+      <c r="F38" s="137"/>
+      <c r="G38" s="137"/>
+      <c r="H38" s="137"/>
+      <c r="I38" s="137"/>
+      <c r="J38" s="137"/>
+      <c r="K38" s="137"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="138"/>
+      <c r="A39" s="143"/>
+      <c r="B39" s="137"/>
+      <c r="C39" s="137"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="137"/>
+      <c r="G39" s="137"/>
+      <c r="H39" s="137"/>
+      <c r="I39" s="137"/>
+      <c r="J39" s="137"/>
+      <c r="K39" s="137"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="138"/>
+      <c r="A40" s="143"/>
+      <c r="B40" s="137"/>
+      <c r="C40" s="137"/>
+      <c r="D40" s="137"/>
+      <c r="E40" s="137"/>
+      <c r="F40" s="137"/>
+      <c r="G40" s="137"/>
+      <c r="H40" s="137"/>
+      <c r="I40" s="137"/>
+      <c r="J40" s="137"/>
+      <c r="K40" s="137"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="138"/>
+      <c r="A41" s="144" t="s">
+        <v>380</v>
+      </c>
+      <c r="B41" s="144"/>
+      <c r="C41" s="144"/>
+      <c r="D41" s="144"/>
+      <c r="E41" s="144"/>
+      <c r="F41" s="144"/>
+      <c r="G41" s="144"/>
+      <c r="H41" s="144"/>
+      <c r="I41" s="144"/>
+      <c r="J41" s="144"/>
+      <c r="K41" s="144"/>
+      <c r="L41" s="144"/>
+      <c r="M41" s="144"/>
+      <c r="N41" s="144"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="138"/>
+      <c r="A42" s="145" t="s">
+        <v>381</v>
+      </c>
+      <c r="B42" s="137"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="137"/>
+      <c r="E42" s="137"/>
+      <c r="F42" s="137"/>
+      <c r="G42" s="137"/>
+      <c r="H42" s="137"/>
+      <c r="I42" s="137"/>
+      <c r="J42" s="137"/>
+      <c r="K42" s="137"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="138"/>
+      <c r="A43" s="145" t="s">
+        <v>382</v>
+      </c>
+      <c r="B43" s="137"/>
+      <c r="C43" s="137"/>
+      <c r="D43" s="137"/>
+      <c r="E43" s="137"/>
+      <c r="F43" s="137"/>
+      <c r="G43" s="137"/>
+      <c r="H43" s="137"/>
+      <c r="I43" s="137"/>
+      <c r="J43" s="137"/>
+      <c r="K43" s="137"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="138"/>
+      <c r="A44" s="146" t="s">
+        <v>383</v>
+      </c>
+      <c r="B44" s="137"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="137"/>
+      <c r="E44" s="137"/>
+      <c r="F44" s="137"/>
+      <c r="G44" s="137"/>
+      <c r="H44" s="137"/>
+      <c r="I44" s="137"/>
+      <c r="J44" s="137"/>
+      <c r="K44" s="137"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="138"/>
+      <c r="A45" s="146" t="s">
+        <v>384</v>
+      </c>
+      <c r="B45" s="137"/>
+      <c r="C45" s="137"/>
+      <c r="D45" s="137"/>
+      <c r="E45" s="137"/>
+      <c r="F45" s="137"/>
+      <c r="G45" s="137"/>
+      <c r="H45" s="137"/>
+      <c r="I45" s="137"/>
+      <c r="J45" s="137"/>
+      <c r="K45" s="137"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="138"/>
+      <c r="A46" s="146" t="s">
+        <v>385</v>
+      </c>
+      <c r="B46" s="137"/>
+      <c r="C46" s="137"/>
+      <c r="D46" s="137"/>
+      <c r="E46" s="137"/>
+      <c r="F46" s="137"/>
+      <c r="G46" s="137"/>
+      <c r="H46" s="137"/>
+      <c r="I46" s="137"/>
+      <c r="J46" s="137"/>
+      <c r="K46" s="137"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="138"/>
+      <c r="A47" s="146" t="s">
+        <v>386</v>
+      </c>
+      <c r="B47" s="137"/>
+      <c r="C47" s="137"/>
+      <c r="D47" s="137"/>
+      <c r="E47" s="137"/>
+      <c r="F47" s="137"/>
+      <c r="G47" s="137"/>
+      <c r="H47" s="137"/>
+      <c r="I47" s="137"/>
+      <c r="J47" s="137"/>
+      <c r="K47" s="137"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="138"/>
+      <c r="A48" s="147" t="s">
+        <v>387</v>
+      </c>
+      <c r="B48" s="137"/>
+      <c r="C48" s="137"/>
+      <c r="D48" s="137"/>
+      <c r="E48" s="137"/>
+      <c r="F48" s="137"/>
+      <c r="G48" s="137"/>
+      <c r="H48" s="137"/>
+      <c r="I48" s="137"/>
+      <c r="J48" s="137"/>
+      <c r="K48" s="137"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="138"/>
+      <c r="A49" s="148" t="s">
+        <v>388</v>
+      </c>
+      <c r="B49" s="137"/>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="137"/>
+      <c r="F49" s="137"/>
+      <c r="G49" s="137"/>
+      <c r="H49" s="137"/>
+      <c r="I49" s="137"/>
+      <c r="J49" s="137"/>
+      <c r="K49" s="137"/>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="138"/>
+      <c r="A50" s="148" t="s">
+        <v>389</v>
+      </c>
+      <c r="B50" s="137"/>
+      <c r="C50" s="137"/>
+      <c r="D50" s="137"/>
+      <c r="E50" s="137"/>
+      <c r="F50" s="137"/>
+      <c r="G50" s="137"/>
+      <c r="H50" s="137"/>
+      <c r="I50" s="137"/>
+      <c r="J50" s="137"/>
+      <c r="K50" s="137"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="138"/>
+      <c r="A51" s="145" t="s">
+        <v>390</v>
+      </c>
+      <c r="B51" s="137"/>
+      <c r="C51" s="137"/>
+      <c r="D51" s="137"/>
+      <c r="E51" s="137"/>
+      <c r="F51" s="137"/>
+      <c r="G51" s="137"/>
+      <c r="H51" s="137"/>
+      <c r="I51" s="137"/>
+      <c r="J51" s="137"/>
+      <c r="K51" s="137"/>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="138"/>
+      <c r="A52" s="145" t="s">
+        <v>391</v>
+      </c>
+      <c r="B52" s="137"/>
+      <c r="C52" s="137"/>
+      <c r="D52" s="137"/>
+      <c r="E52" s="137"/>
+      <c r="F52" s="137"/>
+      <c r="G52" s="137"/>
+      <c r="H52" s="137"/>
+      <c r="I52" s="137"/>
+      <c r="J52" s="137"/>
+      <c r="K52" s="137"/>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="140"/>
+      <c r="A53" s="143"/>
+      <c r="B53" s="137"/>
+      <c r="C53" s="137"/>
+      <c r="D53" s="137"/>
+      <c r="E53" s="137"/>
+      <c r="F53" s="137"/>
+      <c r="G53" s="137"/>
+      <c r="H53" s="137"/>
+      <c r="I53" s="137"/>
+      <c r="J53" s="137"/>
+      <c r="K53" s="137"/>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="138"/>
+      <c r="A54" s="143"/>
+      <c r="B54" s="137"/>
+      <c r="C54" s="137"/>
+      <c r="D54" s="137"/>
+      <c r="E54" s="137"/>
+      <c r="F54" s="137"/>
+      <c r="G54" s="137"/>
+      <c r="H54" s="137"/>
+      <c r="I54" s="137"/>
+      <c r="J54" s="137"/>
+      <c r="K54" s="137"/>
     </row>
     <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="138"/>
+      <c r="A55" s="144" t="s">
+        <v>392</v>
+      </c>
+      <c r="B55" s="144"/>
+      <c r="C55" s="144"/>
+      <c r="D55" s="144"/>
+      <c r="E55" s="144"/>
+      <c r="F55" s="144"/>
+      <c r="G55" s="144"/>
+      <c r="H55" s="144"/>
+      <c r="I55" s="144"/>
+      <c r="J55" s="144"/>
+      <c r="K55" s="144"/>
+      <c r="L55" s="144"/>
+      <c r="M55" s="144"/>
+      <c r="N55" s="144"/>
     </row>
     <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="138"/>
+      <c r="A56" s="149" t="s">
+        <v>393</v>
+      </c>
+      <c r="B56" s="137"/>
+      <c r="C56" s="137"/>
+      <c r="D56" s="137"/>
+      <c r="E56" s="137"/>
+      <c r="F56" s="137"/>
+      <c r="G56" s="137"/>
+      <c r="H56" s="137"/>
+      <c r="I56" s="137"/>
+      <c r="J56" s="137"/>
+      <c r="K56" s="137"/>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="138"/>
+      <c r="A57" s="149" t="s">
+        <v>394</v>
+      </c>
+      <c r="B57" s="137"/>
+      <c r="C57" s="137"/>
+      <c r="D57" s="137"/>
+      <c r="E57" s="137"/>
+      <c r="F57" s="137"/>
+      <c r="G57" s="137"/>
+      <c r="H57" s="137"/>
+      <c r="I57" s="137"/>
+      <c r="J57" s="137"/>
+      <c r="K57" s="137"/>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="138"/>
+      <c r="A58" s="150" t="s">
+        <v>395</v>
+      </c>
+      <c r="B58" s="137"/>
+      <c r="C58" s="137"/>
+      <c r="D58" s="137"/>
+      <c r="E58" s="137"/>
+      <c r="F58" s="137"/>
+      <c r="G58" s="137"/>
+      <c r="H58" s="137"/>
+      <c r="I58" s="137"/>
+      <c r="J58" s="137"/>
+      <c r="K58" s="137"/>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="138"/>
+      <c r="A59" s="150" t="s">
+        <v>396</v>
+      </c>
+      <c r="B59" s="137"/>
+      <c r="C59" s="137"/>
+      <c r="D59" s="137"/>
+      <c r="E59" s="137"/>
+      <c r="F59" s="137"/>
+      <c r="G59" s="137"/>
+      <c r="H59" s="137"/>
+      <c r="I59" s="137"/>
+      <c r="J59" s="137"/>
+      <c r="K59" s="137"/>
+    </row>
+    <row r="60" ht="14.25">
+      <c r="A60" s="150" t="s">
+        <v>397</v>
+      </c>
+      <c r="B60" s="137"/>
+      <c r="C60" s="137"/>
+      <c r="D60" s="137"/>
+      <c r="E60" s="137"/>
+      <c r="F60" s="137"/>
+      <c r="G60" s="137"/>
+      <c r="H60" s="137"/>
+      <c r="I60" s="137"/>
+      <c r="J60" s="137"/>
+      <c r="K60" s="137"/>
+    </row>
+    <row r="61" ht="14.25">
+      <c r="A61" s="150" t="s">
+        <v>398</v>
+      </c>
+      <c r="B61" s="137"/>
+      <c r="C61" s="137"/>
+      <c r="D61" s="137"/>
+      <c r="E61" s="137"/>
+      <c r="F61" s="137"/>
+      <c r="G61" s="137"/>
+      <c r="H61" s="137"/>
+      <c r="I61" s="137"/>
+      <c r="J61" s="137"/>
+      <c r="K61" s="137"/>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="A62" s="151" t="s">
+        <v>399</v>
+      </c>
+      <c r="B62" s="137"/>
+      <c r="C62" s="137"/>
+      <c r="D62" s="137"/>
+      <c r="E62" s="137"/>
+      <c r="F62" s="137"/>
+      <c r="G62" s="137"/>
+      <c r="H62" s="137"/>
+      <c r="I62" s="137"/>
+      <c r="J62" s="137"/>
+      <c r="K62" s="137"/>
+    </row>
+    <row r="63" ht="14.25">
+      <c r="A63" s="152"/>
+      <c r="B63" s="137"/>
+      <c r="C63" s="137"/>
+      <c r="D63" s="137"/>
+      <c r="E63" s="137"/>
+      <c r="F63" s="137"/>
+      <c r="G63" s="137"/>
+      <c r="H63" s="137"/>
+      <c r="I63" s="137"/>
+      <c r="J63" s="137"/>
+      <c r="K63" s="137"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A55:N55"/>
+  </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
